--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_166_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_166_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1531,7 +1531,7 @@
         <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1923,10 +1923,10 @@
         <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3099,16 +3099,16 @@
         <v>22</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
@@ -3295,16 +3295,16 @@
         <v>25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3631,16 +3631,16 @@
         <v>154</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X29" t="n">
         <v>28</v>
@@ -4096,16 +4096,16 @@
         <v>14</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5272,16 +5272,16 @@
         <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>64</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X47" t="n">
         <v>8</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_166_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_166_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>18</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
         <v>19</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3643,14 +3643,14 @@
         <v>9</v>
       </c>
       <c r="X29" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="Y29" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA29" t="n">
@@ -4108,14 +4108,14 @@
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA34" t="n">
@@ -5088,14 +5088,14 @@
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y45" t="n">
         <v>3</v>
       </c>
-      <c r="Y45" t="n">
-        <v>4</v>
-      </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6600,14 +6600,14 @@
         <v>3</v>
       </c>
       <c r="X47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA47" t="n">
